--- a/nickname_song_test.xlsx
+++ b/nickname_song_test.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FEFF20-4572-496D-9BAD-C83263EDA3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30912" windowHeight="17472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
